--- a/resources/HEARTH_Production_Budget_Template.xlsx
+++ b/resources/HEARTH_Production_Budget_Template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="165">
   <si>
     <t xml:space="preserve">HEARTH  ·  Production Budget Template</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t xml:space="preserve">White/warm cells = calculated automatically</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Above the Line</t>
@@ -531,7 +534,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,6 +615,14 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF484858"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -789,11 +800,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -842,7 +857,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -854,7 +869,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -866,31 +881,35 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -902,7 +921,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -910,27 +929,27 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1008,7 +1027,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCDC8BE"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF888898"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF7A4A0A"/>
       <rgbColor rgb="FFF5F0E8"/>
@@ -1234,257 +1253,268 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <f aca="false">'Above the Line'!C27</f>
         <v>0</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5" t="n">
+      <c r="D8" s="7"/>
+      <c r="E8" s="6" t="n">
         <f aca="false">C8-D8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="7"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <f aca="false">'Production Crew'!C22</f>
         <v>0</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="9" t="n">
+      <c r="D9" s="7"/>
+      <c r="E9" s="10" t="n">
         <f aca="false">C9-D9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="10"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <f aca="false">Equipment!C18</f>
         <v>0</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="5" t="n">
+      <c r="D10" s="7"/>
+      <c r="E10" s="6" t="n">
         <f aca="false">C10-D10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="7"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <f aca="false">'Art Department'!C14</f>
         <v>0</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="7"/>
+      <c r="E11" s="10" t="n">
         <f aca="false">C11-D11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <f aca="false">Locations!C14</f>
         <v>0</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="5" t="n">
+      <c r="D12" s="7"/>
+      <c r="E12" s="6" t="n">
         <f aca="false">C12-D12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="7"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <f aca="false">'Post Production'!C16</f>
         <v>0</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="9" t="n">
+      <c r="D13" s="7"/>
+      <c r="E13" s="10" t="n">
         <f aca="false">C13-D13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <f aca="false">Music!C10</f>
         <v>0</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="5" t="n">
+      <c r="D14" s="7"/>
+      <c r="E14" s="6" t="n">
         <f aca="false">C14-D14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="7"/>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <f aca="false">Other!C14</f>
         <v>0</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="9" t="n">
+      <c r="D15" s="7"/>
+      <c r="E15" s="10" t="n">
         <f aca="false">C15-D15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="10"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="13" t="n">
         <f aca="false">SUM(C8:C15)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <f aca="false">SUM(D8:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <f aca="false">C16-D16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="13"/>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <f aca="false">C16*0.1</f>
         <v>0</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="15" t="n">
+      <c r="D17" s="7"/>
+      <c r="E17" s="16" t="n">
         <f aca="false">C17-D17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="16"/>
+      <c r="F17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="19" t="n">
         <f aca="false">C16+C17</f>
         <v>0</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <f aca="false">D16+D17</f>
         <v>0</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="19" t="n">
         <f aca="false">C18-D18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="20" t="s">
+      <c r="F18" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="22" t="s">
+      <c r="C20" s="22"/>
+      <c r="D20" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="23"/>
-      <c r="D21" s="24" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C21" s="24"/>
+      <c r="D21" s="25" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1504,296 +1534,296 @@
   <dimension ref="B1:G25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="26" t="s">
+      <c r="B4" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="C4" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="D4" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="E4" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="F4" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
+      <c r="B5" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="5" t="str">
+      <c r="B6" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="6" t="str">
         <f aca="false">IF(C6="","",C6*D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="9" t="str">
+      <c r="B7" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="10" t="str">
         <f aca="false">IF(C7="","",C7*D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="32"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="5" t="str">
+      <c r="B8" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="6" t="str">
         <f aca="false">IF(C8="","",C8*D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="30"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
+      <c r="B9" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="5" t="str">
+      <c r="B10" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="6" t="str">
         <f aca="false">IF(C10="","",C10*D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="9" t="str">
+      <c r="B11" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="10" t="str">
         <f aca="false">IF(C11="","",C11*D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="5" t="str">
+      <c r="B12" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="6" t="str">
         <f aca="false">IF(C12="","",C12*D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="9" t="str">
+      <c r="B13" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="10" t="str">
         <f aca="false">IF(C13="","",C13*D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="32"/>
+      <c r="G13" s="34"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
+      <c r="B14" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="9" t="str">
+      <c r="B15" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="10" t="str">
         <f aca="false">IF(C15="","",C15*D15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="32"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="5" t="str">
+      <c r="B16" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="6" t="str">
         <f aca="false">IF(C16="","",C16*D16*E16)</f>
         <v/>
       </c>
-      <c r="G16" s="30"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="9" t="str">
+      <c r="B17" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="10" t="str">
         <f aca="false">IF(C17="","",C17*D17*E17)</f>
         <v/>
       </c>
-      <c r="G17" s="32"/>
+      <c r="G17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="5" t="str">
+      <c r="B18" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="6" t="str">
         <f aca="false">IF(C18="","",C18*D18*E18)</f>
         <v/>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="9" t="str">
+      <c r="B19" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="10" t="str">
         <f aca="false">IF(C19="","",C19*D19*E19)</f>
         <v/>
       </c>
-      <c r="G19" s="32"/>
+      <c r="G19" s="34"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="5" t="str">
+      <c r="B20" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="6" t="str">
         <f aca="false">IF(C20="","",C20*D20*E20)</f>
         <v/>
       </c>
-      <c r="G20" s="30"/>
+      <c r="G20" s="32"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="9" t="str">
+      <c r="B21" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="10" t="str">
         <f aca="false">IF(C21="","",C21*D21*E21)</f>
         <v/>
       </c>
-      <c r="G21" s="32"/>
+      <c r="G21" s="34"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="5" t="str">
+      <c r="B22" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="6" t="str">
         <f aca="false">IF(C22="","",C22*D22*E22)</f>
         <v/>
       </c>
-      <c r="G22" s="30"/>
+      <c r="G22" s="32"/>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="34" t="n">
+      <c r="B23" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="36" t="n">
         <f aca="false">SUM(F5:F22)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="34" t="n">
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="36" t="n">
         <f aca="false">SUM(F5:F22)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
+      <c r="G23" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1821,319 +1851,319 @@
   <dimension ref="B1:G27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="36" t="s">
+      <c r="B4" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="C4" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="D4" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="E4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="F4" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="38" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
+      <c r="B5" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="5" t="str">
+      <c r="B6" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="6" t="str">
         <f aca="false">IF(C6="","",C6*D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="9" t="str">
+      <c r="B7" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="10" t="str">
         <f aca="false">IF(C7="","",C7*D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="32"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="5" t="str">
+      <c r="B8" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="6" t="str">
         <f aca="false">IF(C8="","",C8*D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="30"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="9" t="str">
+      <c r="B9" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="10" t="str">
         <f aca="false">IF(C9="","",C9*D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="32"/>
+      <c r="G9" s="34"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="5" t="str">
+      <c r="B10" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="6" t="str">
         <f aca="false">IF(C10="","",C10*D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
+      <c r="B11" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="5" t="str">
+      <c r="B12" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="6" t="str">
         <f aca="false">IF(C12="","",C12*D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="9" t="str">
+      <c r="B13" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="10" t="str">
         <f aca="false">IF(C13="","",C13*D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="32"/>
+      <c r="G13" s="34"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="5" t="str">
+      <c r="B14" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="6" t="str">
         <f aca="false">IF(C14="","",C14*D14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="30"/>
+      <c r="G14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="9" t="str">
+      <c r="B15" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="10" t="str">
         <f aca="false">IF(C15="","",C15*D15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="32"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
+      <c r="B16" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="9" t="str">
+      <c r="B17" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="10" t="str">
         <f aca="false">IF(C17="","",C17*D17*E17)</f>
         <v/>
       </c>
-      <c r="G17" s="32"/>
+      <c r="G17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="5" t="str">
+      <c r="B18" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="6" t="str">
         <f aca="false">IF(C18="","",C18*D18*E18)</f>
         <v/>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
+      <c r="B19" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="5" t="str">
+      <c r="B20" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="6" t="str">
         <f aca="false">IF(C20="","",C20*D20*E20)</f>
         <v/>
       </c>
-      <c r="G20" s="30"/>
+      <c r="G20" s="32"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="9" t="str">
+      <c r="B21" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="10" t="str">
         <f aca="false">IF(C21="","",C21*D21*E21)</f>
         <v/>
       </c>
-      <c r="G21" s="32"/>
+      <c r="G21" s="34"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="5" t="str">
+      <c r="B22" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="6" t="str">
         <f aca="false">IF(C22="","",C22*D22*E22)</f>
         <v/>
       </c>
-      <c r="G22" s="30"/>
+      <c r="G22" s="32"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="9" t="str">
+      <c r="B23" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="10" t="str">
         <f aca="false">IF(C23="","",C23*D23*E23)</f>
         <v/>
       </c>
-      <c r="G23" s="32"/>
+      <c r="G23" s="34"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="5" t="str">
+      <c r="B24" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="6" t="str">
         <f aca="false">IF(C24="","",C24*D24*E24)</f>
         <v/>
       </c>
-      <c r="G24" s="30"/>
+      <c r="G24" s="32"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="34" t="n">
+      <c r="B25" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="36" t="n">
         <f aca="false">SUM(F5:F24)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="34" t="n">
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="36" t="n">
         <f aca="false">SUM(F5:F24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="19"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
+      <c r="G25" s="20"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2162,277 +2192,277 @@
   <dimension ref="B1:G24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="38" t="s">
+      <c r="B4" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="C4" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="D4" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="E4" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="F4" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
+      <c r="B5" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="5" t="str">
+      <c r="B6" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="6" t="str">
         <f aca="false">IF(C6="","",C6*D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="9" t="str">
+      <c r="B7" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="10" t="str">
         <f aca="false">IF(C7="","",C7*D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="32"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="5" t="str">
+      <c r="B8" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="6" t="str">
         <f aca="false">IF(C8="","",C8*D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="30"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="9" t="str">
+      <c r="B9" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="10" t="str">
         <f aca="false">IF(C9="","",C9*D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="32"/>
+      <c r="G9" s="34"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
+      <c r="B10" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="9" t="str">
+      <c r="B11" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="10" t="str">
         <f aca="false">IF(C11="","",C11*D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="5" t="str">
+      <c r="B12" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="6" t="str">
         <f aca="false">IF(C12="","",C12*D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
+      <c r="B13" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="5" t="str">
+      <c r="B14" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="6" t="str">
         <f aca="false">IF(C14="","",C14*D14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="30"/>
+      <c r="G14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="9" t="str">
+      <c r="B15" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="10" t="str">
         <f aca="false">IF(C15="","",C15*D15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="32"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
+      <c r="B16" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="9" t="str">
+      <c r="B17" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="10" t="str">
         <f aca="false">IF(C17="","",C17*D17*E17)</f>
         <v/>
       </c>
-      <c r="G17" s="32"/>
+      <c r="G17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="5" t="str">
+      <c r="B18" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="6" t="str">
         <f aca="false">IF(C18="","",C18*D18*E18)</f>
         <v/>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
+      <c r="B19" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="5" t="str">
+      <c r="B20" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="6" t="str">
         <f aca="false">IF(C20="","",C20*D20*E20)</f>
         <v/>
       </c>
-      <c r="G20" s="30"/>
+      <c r="G20" s="32"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="9" t="str">
+      <c r="B21" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="10" t="str">
         <f aca="false">IF(C21="","",C21*D21*E21)</f>
         <v/>
       </c>
-      <c r="G21" s="32"/>
+      <c r="G21" s="34"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="34" t="n">
+      <c r="B22" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="36" t="n">
         <f aca="false">SUM(F5:F21)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="34" t="n">
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="36" t="n">
         <f aca="false">SUM(F5:F21)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
+      <c r="G22" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2462,221 +2492,221 @@
   <dimension ref="B1:G19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="40" t="s">
+      <c r="B4" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="C4" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="D4" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="E4" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="F4" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="42" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="41" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
+      <c r="B5" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="5" t="str">
+      <c r="B6" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="6" t="str">
         <f aca="false">IF(C6="","",C6*D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="9" t="str">
+      <c r="B7" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="10" t="str">
         <f aca="false">IF(C7="","",C7*D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="32"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="5" t="str">
+      <c r="B8" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="6" t="str">
         <f aca="false">IF(C8="","",C8*D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="30"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="9" t="str">
+      <c r="B9" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="10" t="str">
         <f aca="false">IF(C9="","",C9*D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="32"/>
+      <c r="G9" s="34"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="5" t="str">
+      <c r="B10" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="6" t="str">
         <f aca="false">IF(C10="","",C10*D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="9" t="str">
+      <c r="B11" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="10" t="str">
         <f aca="false">IF(C11="","",C11*D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
+      <c r="B12" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="9" t="str">
+      <c r="B13" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="10" t="str">
         <f aca="false">IF(C13="","",C13*D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="32"/>
+      <c r="G13" s="34"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="5" t="str">
+      <c r="B14" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="6" t="str">
         <f aca="false">IF(C14="","",C14*D14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="30"/>
+      <c r="G14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="9" t="str">
+      <c r="B15" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="10" t="str">
         <f aca="false">IF(C15="","",C15*D15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="32"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="5" t="str">
+      <c r="B16" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="6" t="str">
         <f aca="false">IF(C16="","",C16*D16*E16)</f>
         <v/>
       </c>
-      <c r="G16" s="30"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="34" t="n">
+      <c r="B17" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="36" t="n">
         <f aca="false">SUM(F5:F16)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="34" t="n">
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="36" t="n">
         <f aca="false">SUM(F5:F16)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2703,244 +2733,244 @@
   <dimension ref="B1:G21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="42" t="s">
+      <c r="B4" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="C4" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="D4" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="E4" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="F4" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="44" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
+      <c r="B5" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="5" t="str">
+      <c r="B6" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="6" t="str">
         <f aca="false">IF(C6="","",C6*D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="9" t="str">
+      <c r="B7" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="10" t="str">
         <f aca="false">IF(C7="","",C7*D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="32"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="5" t="str">
+      <c r="B8" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="6" t="str">
         <f aca="false">IF(C8="","",C8*D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="30"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="9" t="str">
+      <c r="B9" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="10" t="str">
         <f aca="false">IF(C9="","",C9*D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="32"/>
+      <c r="G9" s="34"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="5" t="str">
+      <c r="B10" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="6" t="str">
         <f aca="false">IF(C10="","",C10*D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
+      <c r="B11" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="5" t="str">
+      <c r="B12" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="6" t="str">
         <f aca="false">IF(C12="","",C12*D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="9" t="str">
+      <c r="B13" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="10" t="str">
         <f aca="false">IF(C13="","",C13*D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="32"/>
+      <c r="G13" s="34"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="5" t="str">
+      <c r="B14" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="6" t="str">
         <f aca="false">IF(C14="","",C14*D14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="30"/>
+      <c r="G14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="9" t="str">
+      <c r="B15" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="10" t="str">
         <f aca="false">IF(C15="","",C15*D15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="32"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
+      <c r="B16" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="9" t="str">
+      <c r="B17" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="10" t="str">
         <f aca="false">IF(C17="","",C17*D17*E17)</f>
         <v/>
       </c>
-      <c r="G17" s="32"/>
+      <c r="G17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="5" t="str">
+      <c r="B18" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="6" t="str">
         <f aca="false">IF(C18="","",C18*D18*E18)</f>
         <v/>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="34" t="n">
+      <c r="B19" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="36" t="n">
         <f aca="false">SUM(F5:F18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="34" t="n">
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="36" t="n">
         <f aca="false">SUM(F5:F18)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2968,257 +2998,257 @@
   <dimension ref="B1:G22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="44" t="s">
+      <c r="B4" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="C4" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="D4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="E4" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="F4" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="46" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
+      <c r="B5" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="5" t="str">
+      <c r="B6" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="6" t="str">
         <f aca="false">IF(C6="","",C6*D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="9" t="str">
+      <c r="B7" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="10" t="str">
         <f aca="false">IF(C7="","",C7*D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="32"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="5" t="str">
+      <c r="B8" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="6" t="str">
         <f aca="false">IF(C8="","",C8*D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="30"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
+      <c r="B9" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="5" t="str">
+      <c r="B10" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="6" t="str">
         <f aca="false">IF(C10="","",C10*D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="9" t="str">
+      <c r="B11" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="10" t="str">
         <f aca="false">IF(C11="","",C11*D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="5" t="str">
+      <c r="B12" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="6" t="str">
         <f aca="false">IF(C12="","",C12*D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="9" t="str">
+      <c r="B13" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="10" t="str">
         <f aca="false">IF(C13="","",C13*D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="32"/>
+      <c r="G13" s="34"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
+      <c r="B14" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="9" t="str">
+      <c r="B15" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="10" t="str">
         <f aca="false">IF(C15="","",C15*D15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="32"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="5" t="str">
+      <c r="B16" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="6" t="str">
         <f aca="false">IF(C16="","",C16*D16*E16)</f>
         <v/>
       </c>
-      <c r="G16" s="30"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="9" t="str">
+      <c r="B17" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="10" t="str">
         <f aca="false">IF(C17="","",C17*D17*E17)</f>
         <v/>
       </c>
-      <c r="G17" s="32"/>
+      <c r="G17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="5" t="str">
+      <c r="B18" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="6" t="str">
         <f aca="false">IF(C18="","",C18*D18*E18)</f>
         <v/>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="9" t="str">
+      <c r="B19" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="10" t="str">
         <f aca="false">IF(C19="","",C19*D19*E19)</f>
         <v/>
       </c>
-      <c r="G19" s="32"/>
+      <c r="G19" s="34"/>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="34" t="n">
+      <c r="B20" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="36" t="n">
         <f aca="false">SUM(F5:F19)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="34" t="n">
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="36" t="n">
         <f aca="false">SUM(F5:F19)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3246,169 +3276,169 @@
   <dimension ref="B1:G15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="26" t="s">
+      <c r="B4" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="C4" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="D4" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="E4" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="F4" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
+      <c r="B5" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="5" t="str">
+      <c r="B6" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="6" t="str">
         <f aca="false">IF(C6="","",C6*D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="9" t="str">
+      <c r="B7" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="10" t="str">
         <f aca="false">IF(C7="","",C7*D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="32"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
+      <c r="B8" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="9" t="str">
+      <c r="B9" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="10" t="str">
         <f aca="false">IF(C9="","",C9*D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="32"/>
+      <c r="G9" s="34"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="5" t="str">
+      <c r="B10" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="6" t="str">
         <f aca="false">IF(C10="","",C10*D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="9" t="str">
+      <c r="B11" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="10" t="str">
         <f aca="false">IF(C11="","",C11*D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="5" t="str">
+      <c r="B12" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="6" t="str">
         <f aca="false">IF(C12="","",C12*D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="34" t="n">
+      <c r="B13" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="36" t="n">
         <f aca="false">SUM(F5:F12)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="34" t="n">
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="36" t="n">
         <f aca="false">SUM(F5:F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3435,241 +3465,241 @@
   <dimension ref="B1:G21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="46" t="s">
+      <c r="B4" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="C4" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="D4" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="E4" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="F4" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="48" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
+      <c r="B5" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="5" t="str">
+      <c r="B6" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="6" t="str">
         <f aca="false">IF(C6="","",C6*D6*E6)</f>
         <v/>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="9" t="str">
+      <c r="B7" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="10" t="str">
         <f aca="false">IF(C7="","",C7*D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="32"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="5" t="str">
+      <c r="B8" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="6" t="str">
         <f aca="false">IF(C8="","",C8*D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="30"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
+      <c r="B9" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="5" t="str">
+      <c r="B10" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="6" t="str">
         <f aca="false">IF(C10="","",C10*D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="9" t="str">
+      <c r="B11" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="10" t="str">
         <f aca="false">IF(C11="","",C11*D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="5" t="str">
+      <c r="B12" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="6" t="str">
         <f aca="false">IF(C12="","",C12*D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
+      <c r="B13" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="5" t="str">
+      <c r="B14" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="6" t="str">
         <f aca="false">IF(C14="","",C14*D14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="30"/>
+      <c r="G14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="9" t="str">
+      <c r="B15" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="10" t="str">
         <f aca="false">IF(C15="","",C15*D15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="32"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="5" t="str">
+      <c r="B16" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="6" t="str">
         <f aca="false">IF(C16="","",C16*D16*E16)</f>
         <v/>
       </c>
-      <c r="G16" s="30"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="47" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
+      <c r="B17" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="5" t="str">
+      <c r="B18" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="6" t="str">
         <f aca="false">IF(C18="","",C18*D18*E18)</f>
         <v/>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" s="34" t="n">
+      <c r="B19" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="36" t="n">
         <f aca="false">SUM(F5:F18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="34" t="n">
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="36" t="n">
         <f aca="false">SUM(F5:F18)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/resources/HEARTH_Production_Budget_Template.xlsx
+++ b/resources/HEARTH_Production_Budget_Template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="164">
   <si>
     <t xml:space="preserve">HEARTH  ·  Production Budget Template</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t xml:space="preserve">White/warm cells = calculated automatically</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Above the Line</t>
@@ -534,7 +531,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,14 +612,6 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF484858"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -800,15 +789,11 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -857,7 +842,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -869,7 +854,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -881,35 +866,31 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -921,7 +902,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -929,27 +910,27 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1027,7 +1008,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCDC8BE"/>
-      <rgbColor rgb="FF888898"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF7A4A0A"/>
       <rgbColor rgb="FFF5F0E8"/>
@@ -1253,268 +1234,257 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="5" t="n">
         <f aca="false">'Above the Line'!C27</f>
         <v>0</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6" t="n">
+      <c r="D8" s="6"/>
+      <c r="E8" s="5" t="n">
         <f aca="false">C8-D8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="8"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <f aca="false">'Production Crew'!C22</f>
         <v>0</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="10" t="n">
+      <c r="D9" s="6"/>
+      <c r="E9" s="9" t="n">
         <f aca="false">C9-D9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="11"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="5" t="n">
         <f aca="false">Equipment!C18</f>
         <v>0</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="6" t="n">
+      <c r="D10" s="6"/>
+      <c r="E10" s="5" t="n">
         <f aca="false">C10-D10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="8"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <f aca="false">'Art Department'!C14</f>
         <v>0</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="10" t="n">
+      <c r="D11" s="6"/>
+      <c r="E11" s="9" t="n">
         <f aca="false">C11-D11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="11"/>
+      <c r="F11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="5" t="n">
         <f aca="false">Locations!C14</f>
         <v>0</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="6" t="n">
+      <c r="D12" s="6"/>
+      <c r="E12" s="5" t="n">
         <f aca="false">C12-D12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="8"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="9" t="n">
         <f aca="false">'Post Production'!C16</f>
         <v>0</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="10" t="n">
+      <c r="D13" s="6"/>
+      <c r="E13" s="9" t="n">
         <f aca="false">C13-D13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="5" t="n">
         <f aca="false">Music!C10</f>
         <v>0</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="6" t="n">
+      <c r="D14" s="6"/>
+      <c r="E14" s="5" t="n">
         <f aca="false">C14-D14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="8"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="9" t="n">
         <f aca="false">Other!C14</f>
         <v>0</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="10" t="n">
+      <c r="D15" s="6"/>
+      <c r="E15" s="9" t="n">
         <f aca="false">C15-D15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="11"/>
+      <c r="F15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="12" t="n">
         <f aca="false">SUM(C8:C15)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="12" t="n">
         <f aca="false">SUM(D8:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="12" t="n">
         <f aca="false">C16-D16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="14"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="15" t="n">
         <f aca="false">C16*0.1</f>
         <v>0</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="6"/>
+      <c r="E17" s="15" t="n">
         <f aca="false">C17-D17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="17"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="18" t="n">
         <f aca="false">C16+C17</f>
         <v>0</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">D16+D17</f>
         <v>0</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="18" t="n">
         <f aca="false">C18-D18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="20"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="21" t="s">
+      <c r="F18" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="23" t="s">
+      <c r="C20" s="21"/>
+      <c r="D20" s="22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C21" s="24"/>
-      <c r="D21" s="25" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C21" s="23"/>
+      <c r="D21" s="24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1534,296 +1504,296 @@
   <dimension ref="B1:G25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="D4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="E4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="F4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="G4" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="29" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(C6="","",C6*D6*E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="6" t="str">
-        <f aca="false">IF(C6="","",C6*D6*E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="9" t="str">
+        <f aca="false">IF(C7="","",C7*D7*E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(C7="","",C7*D7*E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="5" t="str">
+        <f aca="false">IF(C8="","",C8*D8*E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="30"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="6" t="str">
-        <f aca="false">IF(C8="","",C8*D8*E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="29" t="s">
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(C10="","",C10*D10*E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="6" t="str">
-        <f aca="false">IF(C10="","",C10*D10*E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="9" t="str">
+        <f aca="false">IF(C11="","",C11*D11*E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="32"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="10" t="str">
-        <f aca="false">IF(C11="","",C11*D11*E11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="34"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(C12="","",C12*D12*E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="6" t="str">
-        <f aca="false">IF(C12="","",C12*D12*E12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="9" t="str">
+        <f aca="false">IF(C13="","",C13*D13*E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="32"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="10" t="str">
-        <f aca="false">IF(C13="","",C13*D13*E13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="34"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="29" t="s">
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="9" t="str">
+        <f aca="false">IF(C15="","",C15*D15*E15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="10" t="str">
-        <f aca="false">IF(C15="","",C15*D15*E15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="30" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="5" t="str">
+        <f aca="false">IF(C16="","",C16*D16*E16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="30"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="6" t="str">
-        <f aca="false">IF(C16="","",C16*D16*E16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="32"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="9" t="str">
+        <f aca="false">IF(C17="","",C17*D17*E17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="32"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="10" t="str">
-        <f aca="false">IF(C17="","",C17*D17*E17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="5" t="str">
+        <f aca="false">IF(C18="","",C18*D18*E18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="30"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="6" t="str">
-        <f aca="false">IF(C18="","",C18*D18*E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="33" t="s">
+      <c r="C19" s="6"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="9" t="str">
+        <f aca="false">IF(C19="","",C19*D19*E19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="32"/>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="10" t="str">
-        <f aca="false">IF(C19="","",C19*D19*E19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="34"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="30" t="s">
+      <c r="C20" s="6"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="5" t="str">
+        <f aca="false">IF(C20="","",C20*D20*E20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="30"/>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="6" t="str">
-        <f aca="false">IF(C20="","",C20*D20*E20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="32"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="33" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="9" t="str">
+        <f aca="false">IF(C21="","",C21*D21*E21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="32"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="10" t="str">
-        <f aca="false">IF(C21="","",C21*D21*E21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="34"/>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="s">
+      <c r="C22" s="6"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="5" t="str">
+        <f aca="false">IF(C22="","",C22*D22*E22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="30"/>
+    </row>
+    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="6" t="str">
-        <f aca="false">IF(C22="","",C22*D22*E22)</f>
-        <v/>
-      </c>
-      <c r="G22" s="32"/>
-    </row>
-    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="35" t="s">
+      <c r="C23" s="34" t="n">
+        <f aca="false">SUM(F5:F22)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="34" t="n">
+        <f aca="false">SUM(F5:F22)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="36" t="n">
-        <f aca="false">SUM(F5:F22)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="36" t="n">
-        <f aca="false">SUM(F5:F22)</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1851,319 +1821,319 @@
   <dimension ref="B1:G27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="D4" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="E4" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="F4" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="36" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-    </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(C6="","",C6*D6*E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="6" t="str">
-        <f aca="false">IF(C6="","",C6*D6*E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="9" t="str">
+        <f aca="false">IF(C7="","",C7*D7*E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(C7="","",C7*D7*E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="5" t="str">
+        <f aca="false">IF(C8="","",C8*D8*E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="30"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="6" t="str">
-        <f aca="false">IF(C8="","",C8*D8*E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="9" t="str">
+        <f aca="false">IF(C9="","",C9*D9*E9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="32"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="10" t="str">
-        <f aca="false">IF(C9="","",C9*D9*E9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="34"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(C10="","",C10*D10*E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="6" t="str">
-        <f aca="false">IF(C10="","",C10*D10*E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="39" t="s">
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(C12="","",C12*D12*E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="6" t="str">
-        <f aca="false">IF(C12="","",C12*D12*E12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="9" t="str">
+        <f aca="false">IF(C13="","",C13*D13*E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="32"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="10" t="str">
-        <f aca="false">IF(C13="","",C13*D13*E13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="34"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="s">
+      <c r="C14" s="6"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="5" t="str">
+        <f aca="false">IF(C14="","",C14*D14*E14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="6" t="str">
-        <f aca="false">IF(C14="","",C14*D14*E14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="32"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="9" t="str">
+        <f aca="false">IF(C15="","",C15*D15*E15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="10" t="str">
-        <f aca="false">IF(C15="","",C15*D15*E15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="39" t="s">
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="9" t="str">
+        <f aca="false">IF(C17="","",C17*D17*E17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="32"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="10" t="str">
-        <f aca="false">IF(C17="","",C17*D17*E17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="5" t="str">
+        <f aca="false">IF(C18="","",C18*D18*E18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="30"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="6" t="str">
-        <f aca="false">IF(C18="","",C18*D18*E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="39" t="s">
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="30" t="s">
+      <c r="C20" s="6"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="5" t="str">
+        <f aca="false">IF(C20="","",C20*D20*E20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="30"/>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="6" t="str">
-        <f aca="false">IF(C20="","",C20*D20*E20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="32"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="33" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="9" t="str">
+        <f aca="false">IF(C21="","",C21*D21*E21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="32"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="10" t="str">
-        <f aca="false">IF(C21="","",C21*D21*E21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="34"/>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="s">
+      <c r="C22" s="6"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="5" t="str">
+        <f aca="false">IF(C22="","",C22*D22*E22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="30"/>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="6" t="str">
-        <f aca="false">IF(C22="","",C22*D22*E22)</f>
-        <v/>
-      </c>
-      <c r="G22" s="32"/>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="33" t="s">
+      <c r="C23" s="6"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="9" t="str">
+        <f aca="false">IF(C23="","",C23*D23*E23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="32"/>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="10" t="str">
-        <f aca="false">IF(C23="","",C23*D23*E23)</f>
-        <v/>
-      </c>
-      <c r="G23" s="34"/>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="30" t="s">
+      <c r="C24" s="6"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="5" t="str">
+        <f aca="false">IF(C24="","",C24*D24*E24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="30"/>
+    </row>
+    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="6" t="str">
-        <f aca="false">IF(C24="","",C24*D24*E24)</f>
-        <v/>
-      </c>
-      <c r="G24" s="32"/>
-    </row>
-    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="36" t="n">
+      <c r="C25" s="34" t="n">
         <f aca="false">SUM(F5:F24)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="36" t="n">
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="34" t="n">
         <f aca="false">SUM(F5:F24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
+      <c r="G25" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2192,277 +2162,277 @@
   <dimension ref="B1:G24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="D4" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="E4" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="F4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="38" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-    </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(C6="","",C6*D6*E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="6" t="str">
-        <f aca="false">IF(C6="","",C6*D6*E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="9" t="str">
+        <f aca="false">IF(C7="","",C7*D7*E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(C7="","",C7*D7*E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="5" t="str">
+        <f aca="false">IF(C8="","",C8*D8*E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="30"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="6" t="str">
-        <f aca="false">IF(C8="","",C8*D8*E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="9" t="str">
+        <f aca="false">IF(C9="","",C9*D9*E9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="32"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="10" t="str">
-        <f aca="false">IF(C9="","",C9*D9*E9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="34"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="41" t="s">
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="9" t="str">
+        <f aca="false">IF(C11="","",C11*D11*E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="32"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="10" t="str">
-        <f aca="false">IF(C11="","",C11*D11*E11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="34"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(C12="","",C12*D12*E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="6" t="str">
-        <f aca="false">IF(C12="","",C12*D12*E12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="41" t="s">
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="s">
+      <c r="C14" s="6"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="5" t="str">
+        <f aca="false">IF(C14="","",C14*D14*E14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="6" t="str">
-        <f aca="false">IF(C14="","",C14*D14*E14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="32"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="9" t="str">
+        <f aca="false">IF(C15="","",C15*D15*E15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="10" t="str">
-        <f aca="false">IF(C15="","",C15*D15*E15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="9" t="str">
+        <f aca="false">IF(C17="","",C17*D17*E17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="32"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="10" t="str">
-        <f aca="false">IF(C17="","",C17*D17*E17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="5" t="str">
+        <f aca="false">IF(C18="","",C18*D18*E18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="30"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="6" t="str">
-        <f aca="false">IF(C18="","",C18*D18*E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="41" t="s">
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="30" t="s">
+      <c r="C20" s="6"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="5" t="str">
+        <f aca="false">IF(C20="","",C20*D20*E20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="30"/>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="6" t="str">
-        <f aca="false">IF(C20="","",C20*D20*E20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="32"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="33" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="9" t="str">
+        <f aca="false">IF(C21="","",C21*D21*E21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="32"/>
+    </row>
+    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="10" t="str">
-        <f aca="false">IF(C21="","",C21*D21*E21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="34"/>
-    </row>
-    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="36" t="n">
+      <c r="C22" s="34" t="n">
         <f aca="false">SUM(F5:F21)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="36" t="n">
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="34" t="n">
         <f aca="false">SUM(F5:F21)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2492,221 +2462,221 @@
   <dimension ref="B1:G19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="D4" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="E4" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="F4" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-    </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(C6="","",C6*D6*E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="6" t="str">
-        <f aca="false">IF(C6="","",C6*D6*E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="9" t="str">
+        <f aca="false">IF(C7="","",C7*D7*E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(C7="","",C7*D7*E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="5" t="str">
+        <f aca="false">IF(C8="","",C8*D8*E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="30"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="6" t="str">
-        <f aca="false">IF(C8="","",C8*D8*E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="9" t="str">
+        <f aca="false">IF(C9="","",C9*D9*E9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="32"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="10" t="str">
-        <f aca="false">IF(C9="","",C9*D9*E9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="34"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(C10="","",C10*D10*E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="6" t="str">
-        <f aca="false">IF(C10="","",C10*D10*E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="9" t="str">
+        <f aca="false">IF(C11="","",C11*D11*E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="32"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="10" t="str">
-        <f aca="false">IF(C11="","",C11*D11*E11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="34"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="43" t="s">
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="9" t="str">
+        <f aca="false">IF(C13="","",C13*D13*E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="32"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="10" t="str">
-        <f aca="false">IF(C13="","",C13*D13*E13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="34"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="s">
+      <c r="C14" s="6"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="5" t="str">
+        <f aca="false">IF(C14="","",C14*D14*E14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="6" t="str">
-        <f aca="false">IF(C14="","",C14*D14*E14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="32"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="9" t="str">
+        <f aca="false">IF(C15="","",C15*D15*E15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="10" t="str">
-        <f aca="false">IF(C15="","",C15*D15*E15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="30" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="5" t="str">
+        <f aca="false">IF(C16="","",C16*D16*E16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="30"/>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="6" t="str">
-        <f aca="false">IF(C16="","",C16*D16*E16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="32"/>
-    </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="36" t="n">
+      <c r="C17" s="34" t="n">
         <f aca="false">SUM(F5:F16)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="36" t="n">
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="34" t="n">
         <f aca="false">SUM(F5:F16)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="20"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2733,244 +2703,244 @@
   <dimension ref="B1:G21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="D4" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="E4" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="F4" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="44" t="s">
+      <c r="G4" s="42" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-    </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(C6="","",C6*D6*E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="6" t="str">
-        <f aca="false">IF(C6="","",C6*D6*E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="9" t="str">
+        <f aca="false">IF(C7="","",C7*D7*E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(C7="","",C7*D7*E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="5" t="str">
+        <f aca="false">IF(C8="","",C8*D8*E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="30"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="6" t="str">
-        <f aca="false">IF(C8="","",C8*D8*E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="9" t="str">
+        <f aca="false">IF(C9="","",C9*D9*E9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="32"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="10" t="str">
-        <f aca="false">IF(C9="","",C9*D9*E9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="34"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(C10="","",C10*D10*E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="6" t="str">
-        <f aca="false">IF(C10="","",C10*D10*E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="45" t="s">
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(C12="","",C12*D12*E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="6" t="str">
-        <f aca="false">IF(C12="","",C12*D12*E12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="9" t="str">
+        <f aca="false">IF(C13="","",C13*D13*E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="32"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="10" t="str">
-        <f aca="false">IF(C13="","",C13*D13*E13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="34"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="s">
+      <c r="C14" s="6"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="5" t="str">
+        <f aca="false">IF(C14="","",C14*D14*E14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="6" t="str">
-        <f aca="false">IF(C14="","",C14*D14*E14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="32"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="9" t="str">
+        <f aca="false">IF(C15="","",C15*D15*E15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="10" t="str">
-        <f aca="false">IF(C15="","",C15*D15*E15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="45" t="s">
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="9" t="str">
+        <f aca="false">IF(C17="","",C17*D17*E17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="32"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="10" t="str">
-        <f aca="false">IF(C17="","",C17*D17*E17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="5" t="str">
+        <f aca="false">IF(C18="","",C18*D18*E18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="30"/>
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="6" t="str">
-        <f aca="false">IF(C18="","",C18*D18*E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="36" t="n">
+      <c r="C19" s="34" t="n">
         <f aca="false">SUM(F5:F18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="36" t="n">
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="34" t="n">
         <f aca="false">SUM(F5:F18)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="20"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2998,257 +2968,257 @@
   <dimension ref="B1:G22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="D4" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="E4" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="F4" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="44" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-    </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(C6="","",C6*D6*E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="6" t="str">
-        <f aca="false">IF(C6="","",C6*D6*E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="9" t="str">
+        <f aca="false">IF(C7="","",C7*D7*E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(C7="","",C7*D7*E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="5" t="str">
+        <f aca="false">IF(C8="","",C8*D8*E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="30"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="6" t="str">
-        <f aca="false">IF(C8="","",C8*D8*E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="47" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(C10="","",C10*D10*E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="6" t="str">
-        <f aca="false">IF(C10="","",C10*D10*E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="9" t="str">
+        <f aca="false">IF(C11="","",C11*D11*E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="32"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="10" t="str">
-        <f aca="false">IF(C11="","",C11*D11*E11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="34"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(C12="","",C12*D12*E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="6" t="str">
-        <f aca="false">IF(C12="","",C12*D12*E12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="9" t="str">
+        <f aca="false">IF(C13="","",C13*D13*E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="32"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="10" t="str">
-        <f aca="false">IF(C13="","",C13*D13*E13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="34"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="47" t="s">
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="9" t="str">
+        <f aca="false">IF(C15="","",C15*D15*E15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="10" t="str">
-        <f aca="false">IF(C15="","",C15*D15*E15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="30" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="5" t="str">
+        <f aca="false">IF(C16="","",C16*D16*E16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="30"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="6" t="str">
-        <f aca="false">IF(C16="","",C16*D16*E16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="32"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="9" t="str">
+        <f aca="false">IF(C17="","",C17*D17*E17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="32"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="10" t="str">
-        <f aca="false">IF(C17="","",C17*D17*E17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="5" t="str">
+        <f aca="false">IF(C18="","",C18*D18*E18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="30"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="6" t="str">
-        <f aca="false">IF(C18="","",C18*D18*E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="33" t="s">
+      <c r="C19" s="6"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="9" t="str">
+        <f aca="false">IF(C19="","",C19*D19*E19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="32"/>
+    </row>
+    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="10" t="str">
-        <f aca="false">IF(C19="","",C19*D19*E19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="34"/>
-    </row>
-    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" s="36" t="n">
+      <c r="C20" s="34" t="n">
         <f aca="false">SUM(F5:F19)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="36" t="n">
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="34" t="n">
         <f aca="false">SUM(F5:F19)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="20"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3276,169 +3246,169 @@
   <dimension ref="B1:G15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="D4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="E4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="F4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="26" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(C6="","",C6*D6*E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="6" t="str">
-        <f aca="false">IF(C6="","",C6*D6*E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="9" t="str">
+        <f aca="false">IF(C7="","",C7*D7*E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(C7="","",C7*D7*E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="29" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="9" t="str">
+        <f aca="false">IF(C9="","",C9*D9*E9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="32"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="10" t="str">
-        <f aca="false">IF(C9="","",C9*D9*E9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="34"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(C10="","",C10*D10*E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="6" t="str">
-        <f aca="false">IF(C10="","",C10*D10*E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="9" t="str">
+        <f aca="false">IF(C11="","",C11*D11*E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="32"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="10" t="str">
-        <f aca="false">IF(C11="","",C11*D11*E11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="34"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(C12="","",C12*D12*E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="6" t="str">
-        <f aca="false">IF(C12="","",C12*D12*E12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="36" t="n">
+      <c r="C13" s="34" t="n">
         <f aca="false">SUM(F5:F12)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="36" t="n">
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="34" t="n">
         <f aca="false">SUM(F5:F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3465,241 +3435,241 @@
   <dimension ref="B1:G21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="D4" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="E4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="F4" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="46" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-    </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="5" t="str">
+        <f aca="false">IF(C6="","",C6*D6*E6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="30"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="6" t="str">
-        <f aca="false">IF(C6="","",C6*D6*E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="9" t="str">
+        <f aca="false">IF(C7="","",C7*D7*E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(C7="","",C7*D7*E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="5" t="str">
+        <f aca="false">IF(C8="","",C8*D8*E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="30"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="6" t="str">
-        <f aca="false">IF(C8="","",C8*D8*E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="32"/>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="49" t="s">
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="5" t="str">
+        <f aca="false">IF(C10="","",C10*D10*E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="30"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="6" t="str">
-        <f aca="false">IF(C10="","",C10*D10*E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="9" t="str">
+        <f aca="false">IF(C11="","",C11*D11*E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="32"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="10" t="str">
-        <f aca="false">IF(C11="","",C11*D11*E11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="34"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="5" t="str">
+        <f aca="false">IF(C12="","",C12*D12*E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="6" t="str">
-        <f aca="false">IF(C12="","",C12*D12*E12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="49" t="s">
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="s">
+      <c r="C14" s="6"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="5" t="str">
+        <f aca="false">IF(C14="","",C14*D14*E14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="6" t="str">
-        <f aca="false">IF(C14="","",C14*D14*E14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="32"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="9" t="str">
+        <f aca="false">IF(C15="","",C15*D15*E15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="10" t="str">
-        <f aca="false">IF(C15="","",C15*D15*E15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="30" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="5" t="str">
+        <f aca="false">IF(C16="","",C16*D16*E16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="30"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="6" t="str">
-        <f aca="false">IF(C16="","",C16*D16*E16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="32"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="49" t="s">
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="5" t="str">
+        <f aca="false">IF(C18="","",C18*D18*E18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="30"/>
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="6" t="str">
-        <f aca="false">IF(C18="","",C18*D18*E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="C19" s="36" t="n">
+      <c r="C19" s="34" t="n">
         <f aca="false">SUM(F5:F18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="36" t="n">
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="34" t="n">
         <f aca="false">SUM(F5:F18)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="20"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="6">
